--- a/momentum_summary.xlsx
+++ b/momentum_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shlomiasraf/Desktop/degree/MomentumProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB46C56-66CC-664A-84C2-7D8DBECC4526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C75B422-4985-4648-A917-D5DAC2DEB7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="760" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Wins in Momentum</t>
   </si>
@@ -86,6 +86,30 @@
   </si>
   <si>
     <t>Momentum Switched &amp; Positive Winners</t>
+  </si>
+  <si>
+    <t>Wins Positive Tight</t>
+  </si>
+  <si>
+    <t>Non-Wins Positive Tight</t>
+  </si>
+  <si>
+    <t>Wins Positive not-Tight</t>
+  </si>
+  <si>
+    <t>Non-Wins Positive not-Tight</t>
+  </si>
+  <si>
+    <t>Loss Negative Tight</t>
+  </si>
+  <si>
+    <t>Non-Loss Negative Tight</t>
+  </si>
+  <si>
+    <t>Loss Negative not-Tight</t>
+  </si>
+  <si>
+    <t>Non-Loss Negative not-Tight</t>
   </si>
 </sst>
 </file>
@@ -109,7 +133,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +155,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -162,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -195,6 +225,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -535,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -548,9 +590,17 @@
     <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
@@ -587,8 +637,32 @@
       <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="M1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -625,8 +699,32 @@
       <c r="L2" s="2">
         <v>3</v>
       </c>
+      <c r="M2" s="13">
+        <v>47</v>
+      </c>
+      <c r="N2" s="13">
+        <v>41</v>
+      </c>
+      <c r="O2" s="13">
+        <v>24</v>
+      </c>
+      <c r="P2" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="13">
+        <v>34</v>
+      </c>
+      <c r="R2" s="13">
+        <v>45</v>
+      </c>
+      <c r="S2" s="13">
+        <v>22</v>
+      </c>
+      <c r="T2" s="13">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -663,8 +761,32 @@
       <c r="L3" s="2">
         <v>2</v>
       </c>
+      <c r="M3" s="13">
+        <v>42</v>
+      </c>
+      <c r="N3" s="13">
+        <v>44</v>
+      </c>
+      <c r="O3" s="13">
+        <v>12</v>
+      </c>
+      <c r="P3" s="13">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>42</v>
+      </c>
+      <c r="R3" s="13">
+        <v>47</v>
+      </c>
+      <c r="S3" s="13">
+        <v>15</v>
+      </c>
+      <c r="T3" s="13">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
@@ -701,8 +823,32 @@
       <c r="L4" s="2">
         <v>5</v>
       </c>
+      <c r="M4" s="13">
+        <v>46</v>
+      </c>
+      <c r="N4" s="13">
+        <v>43</v>
+      </c>
+      <c r="O4" s="13">
+        <v>22</v>
+      </c>
+      <c r="P4" s="13">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>51</v>
+      </c>
+      <c r="R4" s="13">
+        <v>40</v>
+      </c>
+      <c r="S4" s="13">
+        <v>17</v>
+      </c>
+      <c r="T4" s="13">
+        <v>19</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -739,8 +885,32 @@
       <c r="L5" s="2">
         <v>6</v>
       </c>
+      <c r="M5" s="13">
+        <v>40</v>
+      </c>
+      <c r="N5" s="13">
+        <v>36</v>
+      </c>
+      <c r="O5" s="13">
+        <v>15</v>
+      </c>
+      <c r="P5" s="13">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>29</v>
+      </c>
+      <c r="R5" s="13">
+        <v>44</v>
+      </c>
+      <c r="S5" s="13">
+        <v>15</v>
+      </c>
+      <c r="T5" s="13">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
@@ -777,57 +947,113 @@
       <c r="L6" s="2">
         <v>8</v>
       </c>
+      <c r="M6" s="13">
+        <v>28</v>
+      </c>
+      <c r="N6" s="13">
+        <v>41</v>
+      </c>
+      <c r="O6" s="13">
+        <v>20</v>
+      </c>
+      <c r="P6" s="13">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>40</v>
+      </c>
+      <c r="R6" s="13">
+        <v>41</v>
+      </c>
+      <c r="S6" s="13">
+        <v>16</v>
+      </c>
+      <c r="T6" s="13">
+        <v>21</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="7">
-        <f>SUM(B2:B6)</f>
+        <f t="shared" ref="B7:G7" si="0">SUM(B2:B6)</f>
         <v>288</v>
       </c>
       <c r="C7" s="7">
-        <f>SUM(C2:C6)</f>
+        <f t="shared" si="0"/>
         <v>309</v>
       </c>
       <c r="D7" s="7">
-        <f>SUM(D2:D6)</f>
+        <f t="shared" si="0"/>
         <v>25.7</v>
       </c>
       <c r="E7" s="7">
-        <f>SUM(E2:E6)</f>
+        <f t="shared" si="0"/>
         <v>261</v>
       </c>
       <c r="F7" s="7">
-        <f>SUM(F2:F6)</f>
+        <f t="shared" si="0"/>
         <v>329</v>
       </c>
       <c r="G7" s="7">
-        <f>SUM(G2:G6)</f>
+        <f t="shared" si="0"/>
         <v>27.589999999999996</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" ref="H7:K7" si="0">SUM(H2:H6)</f>
+        <f t="shared" ref="H7:K7" si="1">SUM(H2:H6)</f>
         <v>1545</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>725</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>256</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" ref="L7" si="1">SUM(L2:L6)</f>
+        <f t="shared" ref="L7:T7" si="2">SUM(L2:L6)</f>
         <v>24</v>
       </c>
+      <c r="M7" s="14">
+        <f t="shared" si="2"/>
+        <v>203</v>
+      </c>
+      <c r="N7" s="14">
+        <f t="shared" si="2"/>
+        <v>205</v>
+      </c>
+      <c r="O7" s="14">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="P7" s="14">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="Q7" s="14">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+      <c r="R7" s="14">
+        <f t="shared" si="2"/>
+        <v>217</v>
+      </c>
+      <c r="S7" s="14">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="T7" s="14">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
@@ -870,6 +1096,38 @@
       <c r="L8" s="4">
         <f>L7 / (J7)</f>
         <v>9.375E-2</v>
+      </c>
+      <c r="M8" s="15">
+        <f>M7 / (N7+M7)</f>
+        <v>0.49754901960784315</v>
+      </c>
+      <c r="N8" s="15">
+        <f>N7 / (M7+N7)</f>
+        <v>0.50245098039215685</v>
+      </c>
+      <c r="O8" s="15">
+        <f>O7 / (P7+O7)</f>
+        <v>0.51381215469613262</v>
+      </c>
+      <c r="P8" s="15">
+        <f>P7 / (O7+P7)</f>
+        <v>0.48618784530386738</v>
+      </c>
+      <c r="Q8" s="15">
+        <f>Q7 / (R7+Q7)</f>
+        <v>0.47457627118644069</v>
+      </c>
+      <c r="R8" s="15">
+        <f>R7 / (Q7+R7)</f>
+        <v>0.52542372881355937</v>
+      </c>
+      <c r="S8" s="15">
+        <f>S7 / (T7+S7)</f>
+        <v>0.46961325966850831</v>
+      </c>
+      <c r="T8" s="15">
+        <f>T7 / (S7+T7)</f>
+        <v>0.53038674033149169</v>
       </c>
     </row>
   </sheetData>

--- a/momentum_summary.xlsx
+++ b/momentum_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shlomiasraf/Desktop/degree/MomentumProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32523E86-BEC8-AB43-9429-ED16E08FE437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B30DC7B-9EE3-C344-96F7-234750C66806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>year</t>
   </si>
@@ -95,13 +95,16 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>24/25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +116,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -550,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -615,113 +624,113 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" s="10">
         <v>0.5</v>
       </c>
       <c r="C2" s="10">
-        <v>0.62</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="D2" s="10">
         <v>0.5</v>
       </c>
       <c r="E2" s="10">
-        <v>0.55800000000000005</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="F2" s="2">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="G2" s="2">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="H2" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="11">
-        <v>0.71299999999999997</v>
+        <v>0.64</v>
       </c>
       <c r="L2" s="11">
-        <v>0.60099999999999998</v>
+        <v>0.64</v>
       </c>
       <c r="M2" s="11">
-        <v>0.70799999999999996</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="N2" s="11">
-        <v>0.53</v>
+        <v>0.55500000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="10">
         <v>0.5</v>
       </c>
       <c r="C3" s="10">
-        <v>0.51700000000000002</v>
+        <v>0.62</v>
       </c>
       <c r="D3" s="10">
         <v>0.5</v>
       </c>
       <c r="E3" s="10">
-        <v>0.54900000000000004</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="F3" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G3" s="2">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="H3" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="11">
-        <v>0.64500000000000002</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="L3" s="11">
-        <v>0.502</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="M3" s="11">
-        <v>0.64400000000000002</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="N3" s="11">
-        <v>0.56200000000000006</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="10">
         <v>0.5</v>
       </c>
       <c r="C4" s="10">
-        <v>0.60499999999999998</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="D4" s="10">
         <v>0.5</v>
       </c>
       <c r="E4" s="10">
-        <v>0.69499999999999995</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="F4" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G4" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H4" s="2">
         <v>51</v>
@@ -730,213 +739,258 @@
         <v>4</v>
       </c>
       <c r="J4" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="11">
-        <v>0.57099999999999995</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="L4" s="11">
-        <v>0.60499999999999998</v>
+        <v>0.502</v>
       </c>
       <c r="M4" s="11">
-        <v>0.65400000000000003</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="N4" s="11">
-        <v>0.72</v>
+        <v>0.56200000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="F5" s="2">
+        <v>305</v>
+      </c>
+      <c r="G5" s="2">
+        <v>143</v>
+      </c>
+      <c r="H5" s="2">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.49099999999999999</v>
-      </c>
-      <c r="F5" s="2">
-        <v>304</v>
-      </c>
-      <c r="G5" s="2">
-        <v>138</v>
-      </c>
-      <c r="H5" s="2">
-        <v>56</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8</v>
-      </c>
       <c r="J5" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="11">
-        <v>0.66400000000000003</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="L5" s="11">
-        <v>0.56799999999999995</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="M5" s="11">
-        <v>0.51400000000000001</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="N5" s="11">
-        <v>0.48899999999999999</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="10">
         <v>0.5</v>
       </c>
       <c r="C6" s="10">
-        <v>0.51</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="D6" s="10">
         <v>0.5</v>
       </c>
       <c r="E6" s="10">
-        <v>0.54900000000000004</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="F6" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="G6" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H6" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" s="11">
-        <v>0.67900000000000005</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="L6" s="11">
-        <v>0.47299999999999998</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="M6" s="11">
-        <v>0.64</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="N6" s="11">
-        <v>0.52600000000000002</v>
+        <v>0.48899999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A7" s="6" t="s">
-        <v>6</v>
+      <c r="A7" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="B7" s="10">
         <v>0.5</v>
       </c>
       <c r="C7" s="10">
-        <f>AVERAGE(C2:C6)</f>
-        <v>0.56699999999999995</v>
+        <v>0.51</v>
       </c>
       <c r="D7" s="10">
-        <f t="shared" ref="D7:E7" si="0">AVERAGE(D2:D6)</f>
         <v>0.5</v>
       </c>
       <c r="E7" s="10">
-        <f t="shared" si="0"/>
-        <v>0.56840000000000002</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" ref="F7:I7" si="1">SUM(F2:F6)</f>
-        <v>1545</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>725</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="1"/>
-        <v>256</v>
-      </c>
-      <c r="I7" s="3">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" ref="J7" si="2">SUM(J2:J6)</f>
-        <v>24</v>
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="F7" s="2">
+        <v>316</v>
+      </c>
+      <c r="G7" s="2">
+        <v>134</v>
+      </c>
+      <c r="H7" s="2">
+        <v>52</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>8</v>
       </c>
       <c r="K7" s="11">
-        <f>AVERAGE(K2:K6)</f>
-        <v>0.65440000000000009</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="L7" s="11">
-        <f t="shared" ref="L7:N7" si="3">AVERAGE(L2:L6)</f>
-        <v>0.54979999999999996</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="3"/>
-        <v>0.6319999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="N7" s="11">
-        <f t="shared" si="3"/>
-        <v>0.56540000000000001</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="10">
+        <f>AVERAGE(C2:C7)</f>
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" ref="D8:E8" si="0">AVERAGE(D3:D7)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="10">
+        <f>AVERAGE(E2:E7)</f>
+        <v>0.5618333333333333</v>
+      </c>
+      <c r="F8" s="3">
+        <f>SUM(F2:F7)</f>
+        <v>1842</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" ref="G8:J8" si="1">SUM(G2:G7)</f>
+        <v>864</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>297</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="K8" s="11">
+        <f>AVERAGE(K2:K7)</f>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="L8" s="11">
+        <f t="shared" ref="L8:N8" si="2">AVERAGE(L2:L7)</f>
+        <v>0.5648333333333333</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="2"/>
+        <v>0.62466666666666659</v>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="2"/>
+        <v>0.56366666666666665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="2">
-        <v>1545</v>
-      </c>
-      <c r="G8" s="4">
-        <f>G7 / (F7)</f>
-        <v>0.46925566343042069</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="4">
+        <f>G8 / (F8)</f>
+        <v>0.46905537459283386</v>
+      </c>
+      <c r="H9" s="2">
         <v>256</v>
       </c>
-      <c r="I8" s="4">
-        <f>I7 / (H7)</f>
-        <v>0.1015625</v>
-      </c>
-      <c r="J8" s="4">
-        <f>J7 / (H7)</f>
-        <v>9.375E-2</v>
-      </c>
-      <c r="K8" s="11" t="s">
+      <c r="I9" s="4">
+        <f>I8 / (H8)</f>
+        <v>9.4276094276094277E-2</v>
+      </c>
+      <c r="J9" s="4">
+        <f>J8 / (H8)</f>
+        <v>9.7643097643097643E-2</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>